--- a/Data from programm.xlsx
+++ b/Data from programm.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,682 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Название</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Сталь</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Температура чугуна</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Масса чугуна</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Масса лома</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Mn</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Высота</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Диаметр</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Сталь</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Standart</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>200.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Сталь 17Г1С</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Сталь 17Г1С</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1324.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Сталь 15Г</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Сталь 15Г</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>320.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1324.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Сталь 05</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Сталь 05</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.16058</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0.01687</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.0168655</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.17513</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.57406</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>290.0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1400.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.16058</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.01687</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.0168655</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.17513</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.57406</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>120.0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.16058</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0.01687</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.0168655</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.17513</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.57406</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Сталь 10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Test 2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.10402</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.00839</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.01247</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.2125</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1.171</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>301.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1395.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.10402</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.00839</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.01247</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.2125</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.171</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.10402</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0.00839</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0.01247</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.2125</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1.171</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>